--- a/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.13.1</t>
+    <t>1.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T11:21:00+00:00</t>
+    <t>2026-05-26T14:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -378,7 +378,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -469,7 +469,7 @@
     <t>information-recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient}
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/information-recipient|0.1.1}
 </t>
   </si>
   <si>
@@ -563,7 +563,7 @@
     <t>basedOn-order-or-requisition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/composition-basedOn-order-or-requisition}
+    <t xml:space="preserve">Extension {http://hl7.eu/fhir/StructureDefinition/composition-basedOn-order-or-requisition|0.1.1}
 </t>
   </si>
   <si>
@@ -710,7 +710,7 @@
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
+    <t>http://hl7.org/fhir/ValueSet/resource-types|4.0.1</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1017,7 +1017,7 @@
     <t>Type of a composition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-typecodes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-typecodes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1056,7 +1056,7 @@
     <t>High-level kind of a clinical document at a macro level.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/document-classcodes</t>
+    <t>http://hl7.org/fhir/ValueSet/document-classcodes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">value:$this}
@@ -1078,7 +1078,7 @@
     <t>studyType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips}
+    <t xml:space="preserve">CodeableConcept {http://hl7.org/fhir/uv/ips/StructureDefinition/CodeableConcept-uv-ips|2.0.0}
 </t>
   </si>
   <si>
@@ -1624,7 +1624,7 @@
     <t>This list of codes represents the main clinical acts being documented.</t>
   </si>
   <si>
-    <t>http://terminology.hl7.org/ValueSet/v3-ActCode</t>
+    <t>http://terminology.hl7.org/ValueSet/v3-ActCode|3.0.0</t>
   </si>
   <si>
     <t>DocumentReference.event.code</t>
@@ -1645,7 +1645,7 @@
     <t>Composition.event.detail</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1731,7 +1731,7 @@
     <t>Classification of a section of a composition/document.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/doc-section-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/doc-section-codes|4.0.1</t>
   </si>
   <si>
     <t>Composition.section.author</t>
@@ -1823,7 +1823,7 @@
     <t>What order applies to the items in the entry.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-order</t>
+    <t>http://hl7.org/fhir/ValueSet/list-order|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].sequenceNumber &gt; 1</t>
@@ -1869,7 +1869,7 @@
     <t>If a section is empty, why it is empty.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-empty-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/list-empty-reason|4.0.1</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ,code&lt;ListEmptyReason].value[type=CD]</t>
@@ -2043,7 +2043,7 @@
     <t>Composition.section.section.author</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Device|Patient|RelatedPerson|Organization)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Device|4.0.1|Patient|4.0.1|RelatedPerson|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>

--- a/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.0</t>
+    <t>1.14.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T14:58:40+00:00</t>
+    <t>2026-07-01T19:23:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.14.1</t>
+    <t>1.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T19:23:08+00:00</t>
+    <t>2026-08-12T07:20:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
+++ b/ig/ch-elm/StructureDefinition-ch-elm-composition-strict.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.15.0</t>
+    <t>1.15.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-12T07:20:00+00:00</t>
+    <t>2026-08-14T07:34:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
